--- a/vfq-dxp-app/reference/VFQ_DXP_Postpaid_Activation_Open_Questions_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Postpaid_Activation_Open_Questions_Reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/parithimalsaravanan/claude-projects/vfq/vfq-dxp-app/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DC9F19-0816-D34E-A054-56A87B47B504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4316A89-1A73-D34C-86DE-DCC84C00883E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1730,7 +1730,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="58" customHeight="1">
+    <row r="2" spans="1:8" ht="58" hidden="1" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>49</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="58" customHeight="1">
+    <row r="3" spans="1:8" ht="58" hidden="1" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>54</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="58" customHeight="1">
+    <row r="4" spans="1:8" ht="58" hidden="1" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>57</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="58" customHeight="1">
+    <row r="5" spans="1:8" ht="58" hidden="1" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>60</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="58" customHeight="1">
+    <row r="6" spans="1:8" ht="58" hidden="1" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>63</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="58" customHeight="1">
+    <row r="7" spans="1:8" ht="58" hidden="1" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>66</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="58" customHeight="1">
+    <row r="8" spans="1:8" ht="58" hidden="1" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>70</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="58" customHeight="1">
+    <row r="9" spans="1:8" ht="58" hidden="1" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>74</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="58" hidden="1" customHeight="1">
+    <row r="25" spans="1:8" ht="58" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>130</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="58" hidden="1" customHeight="1">
+    <row r="26" spans="1:8" ht="58" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>133</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="58" hidden="1" customHeight="1">
+    <row r="27" spans="1:8" ht="58" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>135</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="58" hidden="1" customHeight="1">
+    <row r="28" spans="1:8" ht="58" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>137</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="58" hidden="1" customHeight="1">
+    <row r="29" spans="1:8" ht="58" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>139</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="58" hidden="1" customHeight="1">
+    <row r="30" spans="1:8" ht="58" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>142</v>
       </c>
@@ -2980,7 +2980,7 @@
   <autoFilter ref="A1:H58" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <filterColumn colId="7">
       <filters>
-        <filter val="1"/>
+        <filter val="2"/>
       </filters>
     </filterColumn>
   </autoFilter>
